--- a/bnc-streamlit-app/data/points/424kyd0drjm51x8dsauowgpp0_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/424kyd0drjm51x8dsauowgpp0_playerlog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG19"/>
+  <dimension ref="A1:BG33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -955,14 +955,18 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>RWB</t>
+        </is>
+      </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -970,10 +974,16 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>RWB</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>15</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -991,13 +1001,13 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AG3" t="n">
         <v>1</v>
@@ -1008,21 +1018,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>0.01999425</v>
+        <v>0.5687902499999999</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1031,22 +1041,22 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1078,10 +1088,10 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
         <v>1</v>
@@ -1142,14 +1152,18 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>LWB</t>
+        </is>
+      </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1157,10 +1171,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>LWB</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>15</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -1178,13 +1198,13 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
@@ -1195,45 +1215,45 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>0.01658323</v>
+        <v>0.63303444</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
         <v>4</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -1242,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -1325,14 +1345,18 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>LCM(2)</t>
+        </is>
+      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1340,10 +1364,16 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>LCM(2)</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>15</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1361,13 +1391,13 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1378,83 +1408,83 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.02219132</v>
+        <v>0.7805546</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1512,14 +1542,18 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1527,10 +1561,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>15</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1548,13 +1588,13 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AG6" t="n">
         <v>1</v>
@@ -1565,51 +1605,51 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.02797350999999999</v>
+        <v>1.50481346</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>+0.92</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4</v>
       </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1634,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1695,14 +1735,18 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>CB(3)</t>
+        </is>
+      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1710,10 +1754,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CB(3)</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>15</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1731,13 +1781,13 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
@@ -1748,24 +1798,24 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-0.09638701999999999</v>
+        <v>1.58458609</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>+1.00</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1774,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
@@ -1792,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -1818,13 +1868,13 @@
         </is>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1868,10 +1918,12 @@
           <t>5ga7g20wsa7oqjbh4ijoeknl6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1882,14 +1934,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1897,7 +1949,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1918,16 +1970,16 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1935,83 +1987,83 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>0.02428401</v>
+        <v>1.96128166</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>+1.38</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE8" t="n">
         <v>4</v>
       </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2055,10 +2107,12 @@
           <t>2w7xspkzg7b9ghl20me202ove</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -2069,14 +2123,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2084,7 +2138,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2105,16 +2159,16 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2122,21 +2176,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>-0.006081789999999997</v>
+        <v>0.26193622</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2145,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -2157,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
@@ -2191,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2238,10 +2292,12 @@
           <t>7q96z3aaee5jyccb8pjthi8kp</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -2252,14 +2308,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2267,7 +2323,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2288,16 +2344,16 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2305,21 +2361,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.40638634</v>
+        <v>0.7432465399999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>+0.37</t>
+          <t>+0.16</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2331,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -2349,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2374,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2421,10 +2477,12 @@
           <t>7sdbx7mzjxhvofvke9mp26kbu</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -2435,14 +2493,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2450,7 +2508,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2471,16 +2529,16 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2488,24 +2546,24 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>0.0455227</v>
+        <v>1.41207023</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>+0.83</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2514,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>1</v>
@@ -2532,10 +2590,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -2557,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2604,10 +2662,12 @@
           <t>9psfk94nduz6icnuwty5v9all</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -2618,14 +2678,18 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2633,10 +2697,16 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -2654,16 +2724,16 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2671,83 +2741,83 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>0.15248063</v>
+        <v>0.90391151</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>+0.32</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="BE12" t="n">
         <v>4</v>
       </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2758,37 +2828,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Z. Suzuki</t>
+          <t>N. Aké</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> 5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>LCB(3)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2mfunwzltzdnmzlcjyvx752i</t>
+          <t>7jn9kl5wq29d41ekc2fz2rs2d</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2797,30 +2867,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>80</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>LCB(3)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2832,35 +2906,47 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>N. Aké</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.14670307</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>29</v>
+      </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2875,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -2887,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2910,11 +2996,7 @@
       <c r="BC13" t="n">
         <v>0</v>
       </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
+      <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2922,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2933,37 +3015,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>H. Ito</t>
+          <t>M. Depay</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 21</t>
+          <t xml:space="preserve"> 10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LCB(3)</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8p2yagsx6ujdbmeonkd3u4c89</t>
+          <t>b37h0rc96jh4e34x6iru2plud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2972,33 +3054,47 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>69</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>LCF(2)</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>LCB(3)</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>LCF(2)</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -3007,47 +3103,47 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>H. Ito</t>
+          <t>M. Depay</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>-0.03746078000000001</v>
+        <v>-0.26627822</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AM14" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3056,16 +3152,16 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
@@ -3080,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -3097,12 +3193,16 @@
       <c r="BC14" t="n">
         <v>0</v>
       </c>
-      <c r="BD14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3116,37 +3216,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S. Taniguchi</t>
+          <t>B. Brobbey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3</t>
+          <t xml:space="preserve"> 19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CB(3)</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>954ldw96u7zxzmzdb7fqah80l</t>
+          <t>9c2i7ddl2uh7kuhwq62klkyui</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3155,33 +3255,47 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>84</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>CB(3)</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -3190,47 +3304,47 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>S. Taniguchi</t>
+          <t>B. Brobbey</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>0.27430958</v>
+        <v>0.1258644</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>+0.23</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AM15" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3248,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
@@ -3299,37 +3413,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K. Sano</t>
+          <t>T. Koopmeiners</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 24</t>
+          <t xml:space="preserve"> 20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDM(2)</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6dtp194pewnyuhwkxcn2xpf8q</t>
+          <t>2ugzqrpaooto1r24a6kvqf2ll</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -3338,33 +3452,47 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>69</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>LCM(3)</t>
+        </is>
+      </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>RDM(2)</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>LCM(3)</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -3373,47 +3501,47 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>K. Sano</t>
+          <t>T. Koopmeiners</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>0.01206234</v>
+        <v>0.43291002</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AM16" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3437,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -3482,37 +3610,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D. Kamada</t>
+          <t>Q. Timber</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15</t>
+          <t xml:space="preserve"> 26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LDM(2)</t>
+          <t>RCM(2)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>az15xx7m923srf9gdbwmiyga1</t>
+          <t>e5xuwwa4qs6zxjd7y52tslih</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3521,33 +3649,47 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>69</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>RCM(3)</t>
+        </is>
+      </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>LDM(2)</t>
+          <t>RCM(2)</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>RCM(3)</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -3556,47 +3698,47 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>6duaxcbrofil112qfq4v895go</t>
+          <t>657oha8nkne1ybba2bouzkbo7</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>D. Kamada</t>
+          <t>Q. Timber</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>-0.10805102</v>
+        <v>0.22308518</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AM17" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3605,22 +3747,22 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -3651,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3670,17 +3812,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Ueda</t>
+          <t>Z. Suzuki</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3690,12 +3832,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8d0ffyx2qnnp0limf5aou92ei</t>
+          <t>2mfunwzltzdnmzlcjyvx752i</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3712,22 +3854,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3748,10 +3890,10 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3759,55 +3901,43 @@
       <c r="AG18" t="n">
         <v>1</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>A. Ueda</t>
-        </is>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.11771897</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>+0.08</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>4</v>
       </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
@@ -3829,15 +3959,19 @@
       <c r="BC18" t="n">
         <v>0</v>
       </c>
-      <c r="BD18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3853,17 +3987,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D. Maeda</t>
+          <t>R. Doan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11</t>
+          <t xml:space="preserve"> 10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAM(2)</t>
+          <t>RWB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3873,18 +4007,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4x7o9h6ea8ldt9sxgz87vwycp</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>7o11dzx2cccrslutrjl16ik89</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -3895,22 +4031,22 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>LAM(2)</t>
+          <t>RWB</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3931,38 +4067,38 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>D. Maeda</t>
+          <t>R. Doan</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>-0.001892700000000011</v>
+        <v>0.11900773</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3977,16 +4113,16 @@
         <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -4020,6 +4156,2626 @@
         <v>1</v>
       </c>
       <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>K. Nakamura</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LWB</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8wq90yejo2ktnfuzrkju45all</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>96</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>96</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>LWB</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>96</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>K. Nakamura</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.28098484</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>+0.70</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>H. Ito</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LCB(3)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8p2yagsx6ujdbmeonkd3u4c89</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>96</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>96</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>LCB(3)</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>96</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>H. Ito</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.03592874999999994</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>S. Taniguchi</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CB(3)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>954ldw96u7zxzmzdb7fqah80l</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>96</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>96</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>CB(3)</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>96</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>S. Taniguchi</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.04879944</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>+0.47</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>T. Watanabe</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6fdwd71dx2qu7uzzs3ozm9x7u</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>74</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>74</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>74</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>T. Watanabe</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.50772841</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>K. Sano</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RDM(2)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6dtp194pewnyuhwkxcn2xpf8q</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>96</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>96</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>RDM(2)</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>96</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>K. Sano</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>-0.08280394000000001</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D. Kamada</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LDM(2)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>az15xx7m923srf9gdbwmiyga1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>96</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>96</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>LDM(2)</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>96</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>D. Kamada</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.23531933</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>+0.65</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A. Ueda</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>8d0ffyx2qnnp0limf5aou92ei</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>83</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>LAM(2)</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>83</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>LAM(2)</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>A. Ueda</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.5394303499999999</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>83</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T. Kubo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAM(2)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1qkep5ck252k1g3oqza5ygh61</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>74</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>LAM(2)</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>74</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>RAM(2)</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>LAM(2)</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>T. Kubo</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.5734215599999999</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>D. Maeda</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LAM(2)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4x7o9h6ea8ldt9sxgz87vwycp</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>65</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>65</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>LAM(2)</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>65</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>D. Maeda</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.22970903</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y. Sugawara</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RWB</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ad2qplv0aa66l11ipq6yh0hd5</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>74</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>22</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>96</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>RWB</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>22</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Y. Sugawara</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.53128946</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>J. Ito</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 14</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAM(2)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>cmrdm4nnd62inlvsnc52vkicp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>31</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>96</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>RAM(2)</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>31</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>J. Ito</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.4718419200000001</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K. Ogawa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 19</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAM(2)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>dgex06nxjy9fdvc12o8keg99l</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>74</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>22</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>96</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>RAM(2)</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>K. Ogawa</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.7682624199999999</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>+0.19</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>T. Tomiyasu</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 22</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2922aevmtpw4qvcwohmxmqtbd</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>74</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>22</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>96</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>22</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>T. Tomiyasu</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>-0.04664069999999997</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>424kyd0drjm51x8dsauowgpp0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>K. Shiogai</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 26</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>32ko5zzk7805mp4q4n3iwiihg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>83</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>96</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>13</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>6duaxcbrofil112qfq4v895go</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>K. Shiogai</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.02980165</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>83</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
         <v>0</v>
       </c>
     </row>
